--- a/爆チャリ仕様書.xlsx
+++ b/爆チャリ仕様書.xlsx
@@ -12,7 +12,10 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="プレイヤー" sheetId="1" r:id="rId1"/>
+    <sheet name="シーン" sheetId="4" r:id="rId2"/>
+    <sheet name="乗り物" sheetId="2" r:id="rId3"/>
+    <sheet name="ステージ" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -21,6 +24,150 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+  <si>
+    <t>挙動</t>
+    <rPh sb="0" eb="2">
+      <t>キョドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スクロール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当たり判定</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>操作方法</t>
+    <rPh sb="0" eb="4">
+      <t>ソウサホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>R：リスタート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自転車</t>
+    <rPh sb="0" eb="3">
+      <t>ジテンシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスク</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイヤの回転</t>
+    <rPh sb="4" eb="6">
+      <t>カイテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>絵</t>
+    <rPh sb="0" eb="1">
+      <t>エ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスク</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゴール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージセレクト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリア画面（仮）</t>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死亡</t>
+    <rPh sb="0" eb="2">
+      <t>シボウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↑(W)：前</t>
+    <rPh sb="5" eb="6">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↓(S)：後ろ</t>
+    <rPh sb="5" eb="6">
+      <t>ウシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→(D)：右回り（慣性）</t>
+    <rPh sb="5" eb="7">
+      <t>ミギマワ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>←(A)：左回り（慣性）</t>
+    <rPh sb="5" eb="7">
+      <t>ヒダリマワ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スペース：ジャンプ（仮）</t>
+    <rPh sb="10" eb="11">
+      <t>カリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇×</t>
+    <phoneticPr fontId="1"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -348,12 +495,153 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.875" customWidth="1"/>
+    <col min="3" max="3" width="11.25" customWidth="1"/>
+    <col min="4" max="4" width="27.125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="21.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="15.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/爆チャリ仕様書.xlsx
+++ b/爆チャリ仕様書.xlsx
@@ -12,10 +12,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120"/>
   </bookViews>
   <sheets>
-    <sheet name="プレイヤー" sheetId="1" r:id="rId1"/>
-    <sheet name="シーン" sheetId="4" r:id="rId2"/>
-    <sheet name="乗り物" sheetId="2" r:id="rId3"/>
-    <sheet name="ステージ" sheetId="3" r:id="rId4"/>
+    <sheet name="α分" sheetId="5" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,20 +24,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
-  <si>
-    <t>挙動</t>
-    <rPh sb="0" eb="2">
-      <t>キョドウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="34">
   <si>
     <t>スクロール</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -72,17 +58,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>タスク</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>タイヤの回転</t>
-    <rPh sb="4" eb="6">
-      <t>カイテン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>絵</t>
     <rPh sb="0" eb="1">
       <t>エ</t>
@@ -90,14 +65,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>タスク</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ゴール</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>タイトル</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -106,65 +73,143 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>クリア画面（仮）</t>
+    <t>左右移動</t>
+    <rPh sb="0" eb="4">
+      <t>サユウイドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回転</t>
+    <rPh sb="0" eb="2">
+      <t>カイテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダッシュ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>△</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>×</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>△</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死亡判定</t>
+    <rPh sb="0" eb="4">
+      <t>シボウハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリア判定</t>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>システム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージセレクト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤー乗車</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>×</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>×</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>△</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>×</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ１</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリア画面</t>
     <rPh sb="3" eb="5">
       <t>ガメン</t>
     </rPh>
-    <rPh sb="6" eb="7">
-      <t>カリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>死亡</t>
-    <rPh sb="0" eb="2">
-      <t>シボウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>↑(W)：前</t>
-    <rPh sb="5" eb="6">
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>W：前</t>
+    <rPh sb="2" eb="3">
       <t>マエ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>↓(S)：後ろ</t>
-    <rPh sb="5" eb="6">
+    <t>S：後ろ</t>
+    <rPh sb="2" eb="3">
       <t>ウシ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>→(D)：右回り（慣性）</t>
-    <rPh sb="5" eb="7">
+    <t>D：右回り（慣性）</t>
+    <rPh sb="2" eb="4">
       <t>ミギマワ</t>
     </rPh>
-    <rPh sb="9" eb="11">
+    <rPh sb="6" eb="8">
       <t>カンセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>←(A)：左回り（慣性）</t>
-    <rPh sb="5" eb="7">
+    <t>A：左回り（慣性）</t>
+    <rPh sb="2" eb="4">
       <t>ヒダリマワ</t>
     </rPh>
-    <rPh sb="9" eb="11">
+    <rPh sb="6" eb="8">
       <t>カンセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>スペース：ジャンプ（仮）</t>
-    <rPh sb="10" eb="11">
-      <t>カリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>〇×</t>
+    <t>シフト：ダッシュ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -172,7 +217,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,6 +233,15 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -197,7 +251,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -205,15 +259,154 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -495,153 +688,233 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.875" customWidth="1"/>
-    <col min="3" max="3" width="11.25" customWidth="1"/>
-    <col min="4" max="4" width="27.125" customWidth="1"/>
+    <col min="1" max="1" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="9"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="1"/>
+    </row>
+    <row r="6" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="9"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="1"/>
+    </row>
+    <row r="12" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B12" s="9"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="18" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B18" s="1"/>
+    </row>
+    <row r="19" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="9"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A21" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B25" s="1"/>
+    </row>
+    <row r="26" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="9"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A27" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="D6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="D7" t="s">
-        <v>20</v>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A26:B26"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="21.375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="2" max="2" width="15.375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/爆チャリ仕様書.xlsx
+++ b/爆チャリ仕様書.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="34">
   <si>
     <t>スクロール</t>
     <phoneticPr fontId="1"/>
@@ -95,15 +95,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>△</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>×</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>△</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -210,6 +202,17 @@
   </si>
   <si>
     <t>シフト：ダッシュ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>制限時間</t>
+    <rPh sb="0" eb="4">
+      <t>セイゲンジカン</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -251,7 +254,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -371,13 +374,65 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -407,6 +462,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -688,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.75" bestFit="1" customWidth="1"/>
@@ -697,7 +767,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B1" s="9"/>
     </row>
@@ -706,15 +776,15 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -722,7 +792,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -739,7 +809,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
@@ -747,7 +817,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -755,7 +825,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -763,7 +833,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -777,58 +847,58 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B18" s="1"/>
     </row>
     <row r="19" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="9"/>
+      <c r="A19" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="11"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A20" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="5" t="s">
+      <c r="A20" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="13" t="s">
         <v>11</v>
       </c>
     </row>
@@ -842,67 +912,73 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A24" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B25" s="1"/>
-    </row>
-    <row r="26" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="9"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A27" s="4" t="s">
+      <c r="A25" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="28" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" s="9"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A29" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A28" s="2" t="s">
+      <c r="B29" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A30" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A29" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>21</v>
+      <c r="B30" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A31" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -911,7 +987,7 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/爆チャリ仕様書.xlsx
+++ b/爆チャリ仕様書.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
   <si>
     <t>スクロール</t>
     <phoneticPr fontId="1"/>
@@ -95,10 +95,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>×</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -125,25 +121,10 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>プレイヤー乗車</t>
-    <rPh sb="5" eb="7">
-      <t>ジョウシャ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>×</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>×</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>△</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>シーン</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -152,18 +133,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>×</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ステージ１</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>クリア画面</t>
-    <rPh sb="3" eb="5">
-      <t>ガメン</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -213,6 +183,22 @@
     <rPh sb="0" eb="4">
       <t>セイゲンジカン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -457,6 +443,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -468,15 +463,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -766,25 +752,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="9"/>
+      <c r="A1" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="12"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -792,17 +778,17 @@
         <v>5</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="1"/>
     </row>
     <row r="6" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="9"/>
+      <c r="B6" s="12"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
@@ -825,7 +811,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -840,14 +826,14 @@
       <c r="B11" s="1"/>
     </row>
     <row r="12" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="9"/>
+      <c r="B12" s="12"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>11</v>
@@ -855,15 +841,15 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>11</v>
@@ -871,7 +857,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>11</v>
@@ -879,26 +865,26 @@
     </row>
     <row r="17" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B18" s="1"/>
     </row>
     <row r="19" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="11"/>
+      <c r="A19" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="14"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A20" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" s="13" t="s">
+      <c r="A20" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>11</v>
       </c>
     </row>
@@ -912,19 +898,15 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A23" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="A23" s="2"/>
+      <c r="B23" s="6"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" s="2" t="s">
@@ -935,8 +917,8 @@
       </c>
     </row>
     <row r="25" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="14" t="s">
-        <v>33</v>
+      <c r="A25" s="10" t="s">
+        <v>27</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>11</v>
@@ -944,17 +926,17 @@
     </row>
     <row r="27" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="28" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="9"/>
+      <c r="A28" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" s="12"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
@@ -962,23 +944,19 @@
         <v>7</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A31" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="A31" s="2"/>
+      <c r="B31" s="6"/>
     </row>
     <row r="32" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A32" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/爆チャリ仕様書.xlsx
+++ b/爆チャリ仕様書.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="83">
   <si>
     <t>スクロール</t>
     <phoneticPr fontId="1"/>
@@ -51,6 +51,336 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>タイトル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージセレクト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左右移動</t>
+    <rPh sb="0" eb="4">
+      <t>サユウイドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回転</t>
+    <rPh sb="0" eb="2">
+      <t>カイテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダッシュ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死亡判定</t>
+    <rPh sb="0" eb="4">
+      <t>シボウハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリア判定</t>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>システム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージセレクト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ１</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>W：前</t>
+    <rPh sb="2" eb="3">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>S：後ろ</t>
+    <rPh sb="2" eb="3">
+      <t>ウシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D：右回り（慣性）</t>
+    <rPh sb="2" eb="4">
+      <t>ミギマワ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A：左回り（慣性）</t>
+    <rPh sb="2" eb="4">
+      <t>ヒダリマワ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シフト：ダッシュ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>制限時間</t>
+    <rPh sb="0" eb="4">
+      <t>セイゲンジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ２</t>
+  </si>
+  <si>
+    <t>ステージ３</t>
+  </si>
+  <si>
+    <t>ステージ４</t>
+  </si>
+  <si>
+    <t>ステージ５</t>
+  </si>
+  <si>
+    <t>ステージ６</t>
+  </si>
+  <si>
+    <t>ステージ７</t>
+  </si>
+  <si>
+    <t>ステージ８</t>
+  </si>
+  <si>
+    <t>ステージ９</t>
+  </si>
+  <si>
+    <t>ステージ１０</t>
+  </si>
+  <si>
+    <t>×</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>×</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ランキング</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>×</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遊び方</t>
+    <rPh sb="0" eb="1">
+      <t>アソ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>×</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BGM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトル画面</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージセレクト画面</t>
+    <rPh sb="8" eb="10">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遊び方画面</t>
+    <rPh sb="0" eb="1">
+      <t>アソ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ランキング画面</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ１</t>
+  </si>
+  <si>
+    <t>効果音</t>
+    <rPh sb="0" eb="3">
+      <t>コウカオン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームクリア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームオーバー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>衝突音</t>
+    <rPh sb="0" eb="2">
+      <t>ショウトツ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動中の音</t>
+    <rPh sb="0" eb="3">
+      <t>イドウチュウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダッシュの音</t>
+    <rPh sb="5" eb="6">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スタミナ切れの音</t>
+    <rPh sb="4" eb="5">
+      <t>ギ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>橋の音</t>
+    <rPh sb="0" eb="1">
+      <t>ハシ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死ぬ床の音</t>
+    <rPh sb="0" eb="1">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ユカ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダッシュ版の音</t>
+    <rPh sb="4" eb="5">
+      <t>バン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>つららの音</t>
+    <rPh sb="4" eb="5">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボタンのクリック音</t>
+    <rPh sb="8" eb="9">
+      <t>オン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イラスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>自転車</t>
     <rPh sb="0" eb="3">
       <t>ジテンシャ</t>
@@ -58,130 +388,111 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>絵</t>
+    <t>プレイヤー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダッシュ版</t>
+    <rPh sb="4" eb="5">
+      <t>バン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動する床</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ユカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死亡する床</t>
+    <rPh sb="0" eb="2">
+      <t>シボウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ユカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スタミナゲージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ背景</t>
+    <rPh sb="4" eb="6">
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトル背景</t>
+    <rPh sb="4" eb="6">
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージセレクト背景</t>
+    <rPh sb="8" eb="10">
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遊び方背景</t>
     <rPh sb="0" eb="1">
-      <t>エ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>タイトル</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ステージセレクト</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>左右移動</t>
-    <rPh sb="0" eb="4">
-      <t>サユウイドウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>回転</t>
-    <rPh sb="0" eb="2">
-      <t>カイテン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ダッシュ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>〇</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プレイヤー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>死亡判定</t>
-    <rPh sb="0" eb="4">
-      <t>シボウハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>クリア判定</t>
+      <t>アソ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カタ</t>
+    </rPh>
     <rPh sb="3" eb="5">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>システム</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ステージセレクト</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>×</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>シーン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>〇</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ステージ１</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>W：前</t>
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スタートボタン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遊び方ボタン</t>
+    <rPh sb="0" eb="1">
+      <t>アソ</t>
+    </rPh>
     <rPh sb="2" eb="3">
-      <t>マエ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>S：後ろ</t>
-    <rPh sb="2" eb="3">
-      <t>ウシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>D：右回り（慣性）</t>
-    <rPh sb="2" eb="4">
-      <t>ミギマワ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>カンセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>A：左回り（慣性）</t>
-    <rPh sb="2" eb="4">
-      <t>ヒダリマワ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>カンセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>シフト：ダッシュ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>〇</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>制限時間</t>
-    <rPh sb="0" eb="4">
-      <t>セイゲンジカン</t>
+      <t>カタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セレクトボタン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戻るボタン</t>
+    <rPh sb="0" eb="1">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ランキングボタン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EXITボタン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鳥</t>
+    <rPh sb="0" eb="1">
+      <t>トリ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -206,7 +517,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -231,6 +542,14 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -240,7 +559,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -312,95 +631,17 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -418,12 +659,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
@@ -431,38 +669,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -744,228 +982,548 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="18.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="3.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="D1" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="9"/>
+      <c r="G1" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="9"/>
+      <c r="J1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="9"/>
+      <c r="M1" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="N1" s="9"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A2" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="12"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="H2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N6" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="9"/>
+      <c r="J8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="K9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="1"/>
-    </row>
-    <row r="6" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="12"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A8" s="2" t="s">
+      <c r="E10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N10" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="1"/>
-    </row>
-    <row r="12" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="B12" s="12"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A13" s="4" t="s">
+      <c r="J11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N11" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A14" s="2" t="s">
+      <c r="E12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N12" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="1"/>
-    </row>
-    <row r="19" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="14"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A20" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A21" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A23" s="2"/>
-      <c r="B23" s="6"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A24" s="2" t="s">
+      <c r="E13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N13" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="28" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28" s="12"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A29" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A30" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A31" s="2"/>
-      <c r="B31" s="6"/>
-    </row>
-    <row r="32" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>30</v>
+      <c r="E14" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N14" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N15" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="N18" s="9"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="M19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="N19" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="M20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N20" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="M21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="M22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N22" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="M23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N23" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="M24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="N24" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="M25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N25" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="M26" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N26" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="M27" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N27" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="M28" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N28" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="M29" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="N29" s="12" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D1:E1"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/爆チャリ仕様書.xlsx
+++ b/爆チャリ仕様書.xlsx
@@ -1292,7 +1292,7 @@
         <v>33</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>31</v>

--- a/爆チャリ仕様書.xlsx
+++ b/爆チャリ仕様書.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="94">
   <si>
     <t>スクロール</t>
     <phoneticPr fontId="1"/>
@@ -506,6 +506,74 @@
   </si>
   <si>
     <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ギミック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>動く床</t>
+    <rPh sb="0" eb="1">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ユカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>橋</t>
+    <rPh sb="0" eb="1">
+      <t>ハシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死ぬ地面</t>
+    <rPh sb="0" eb="1">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>つらら</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回転床</t>
+    <rPh sb="0" eb="3">
+      <t>カイテンユカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>歯車</t>
+    <rPh sb="0" eb="2">
+      <t>ハグルマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダッシュ版</t>
+    <rPh sb="4" eb="5">
+      <t>バン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ばね</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>×</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -559,7 +627,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -653,13 +721,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -684,12 +782,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -701,6 +793,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -998,32 +1102,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="D1" s="8" t="s">
+      <c r="B1" s="13"/>
+      <c r="D1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="9"/>
-      <c r="G1" s="8" t="s">
+      <c r="E1" s="13"/>
+      <c r="G1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="9"/>
-      <c r="J1" s="8" t="s">
+      <c r="H1" s="13"/>
+      <c r="J1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="9"/>
-      <c r="M1" s="8" t="s">
+      <c r="K1" s="13"/>
+      <c r="M1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="N1" s="9"/>
+      <c r="N1" s="13"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="9" t="s">
         <v>79</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -1047,7 +1151,7 @@
       <c r="M2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="N2" s="8" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1055,7 +1159,7 @@
       <c r="A3" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="9" t="s">
         <v>79</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1079,7 +1183,7 @@
       <c r="M3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="N3" s="8" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1087,7 +1191,7 @@
       <c r="A4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>82</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -1105,13 +1209,13 @@
       <c r="J4" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="8" t="s">
         <v>23</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="10" t="s">
+      <c r="N4" s="8" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1119,7 +1223,7 @@
       <c r="A5" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>42</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -1143,7 +1247,7 @@
       <c r="M5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N5" s="10" t="s">
+      <c r="N5" s="8" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1151,7 +1255,7 @@
       <c r="A6" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="9" t="s">
         <v>42</v>
       </c>
       <c r="D6" s="2" t="s">
@@ -1175,7 +1279,7 @@
       <c r="M6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N6" s="10" t="s">
+      <c r="N6" s="8" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1183,7 +1287,7 @@
       <c r="A7" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="9" t="s">
         <v>79</v>
       </c>
       <c r="J7" s="1" t="s">
@@ -1195,7 +1299,7 @@
       <c r="M7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="N7" s="10" t="s">
+      <c r="N7" s="8" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1203,13 +1307,17 @@
       <c r="A8" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="E8" s="9"/>
+      <c r="E8" s="13"/>
+      <c r="G8" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H8" s="15"/>
       <c r="J8" s="1" t="s">
         <v>30</v>
       </c>
@@ -1219,7 +1327,7 @@
       <c r="M8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N8" s="10" t="s">
+      <c r="N8" s="8" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1227,7 +1335,7 @@
       <c r="A9" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="9" t="s">
         <v>80</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -1236,6 +1344,12 @@
       <c r="E9" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="G9" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="J9" s="1" t="s">
         <v>31</v>
       </c>
@@ -1245,7 +1359,7 @@
       <c r="M9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="N9" s="10" t="s">
+      <c r="N9" s="8" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1253,7 +1367,7 @@
       <c r="A10" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="9" t="s">
         <v>42</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -1262,6 +1376,12 @@
       <c r="E10" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="G10" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="J10" s="1" t="s">
         <v>32</v>
       </c>
@@ -1271,7 +1391,7 @@
       <c r="M10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N10" s="10" t="s">
+      <c r="N10" s="8" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1279,7 +1399,7 @@
       <c r="A11" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="9" t="s">
         <v>42</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -1288,6 +1408,12 @@
       <c r="E11" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="G11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="J11" s="1" t="s">
         <v>33</v>
       </c>
@@ -1297,7 +1423,7 @@
       <c r="M11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N11" s="10" t="s">
+      <c r="N11" s="8" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1305,7 +1431,7 @@
       <c r="A12" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="9" t="s">
         <v>81</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -1314,6 +1440,12 @@
       <c r="E12" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="G12" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="J12" s="1" t="s">
         <v>34</v>
       </c>
@@ -1323,7 +1455,7 @@
       <c r="M12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="N12" s="10" t="s">
+      <c r="N12" s="8" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1331,7 +1463,7 @@
       <c r="A13" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="9" t="s">
         <v>79</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -1340,6 +1472,12 @@
       <c r="E13" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="G13" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="J13" s="1" t="s">
         <v>35</v>
       </c>
@@ -1349,7 +1487,7 @@
       <c r="M13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="N13" s="10" t="s">
+      <c r="N13" s="8" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1357,7 +1495,7 @@
       <c r="A14" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="9" t="s">
         <v>42</v>
       </c>
       <c r="D14" s="2" t="s">
@@ -1366,6 +1504,12 @@
       <c r="E14" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="G14" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="J14" s="2" t="s">
         <v>36</v>
       </c>
@@ -1375,7 +1519,7 @@
       <c r="M14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N14" s="10" t="s">
+      <c r="N14" s="8" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1383,13 +1527,19 @@
       <c r="A15" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="9" t="s">
         <v>79</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>93</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="N15" s="10" t="s">
+      <c r="N15" s="8" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1397,8 +1547,14 @@
       <c r="A16" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="9" t="s">
         <v>79</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>92</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>36</v>
@@ -1411,7 +1567,7 @@
       <c r="A17" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="9" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1419,19 +1575,19 @@
       <c r="A18" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B18" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="M18" s="8" t="s">
+      <c r="B18" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="M18" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="N18" s="9"/>
+      <c r="N18" s="13"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M19" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="N19" s="11" t="s">
+      <c r="N19" s="9" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1439,7 +1595,7 @@
       <c r="M20" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="N20" s="11" t="s">
+      <c r="N20" s="9" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1447,7 +1603,7 @@
       <c r="M21" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="N21" s="11" t="s">
+      <c r="N21" s="9" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1455,7 +1611,7 @@
       <c r="M22" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="N22" s="11" t="s">
+      <c r="N22" s="9" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1463,7 +1619,7 @@
       <c r="M23" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="N23" s="11" t="s">
+      <c r="N23" s="9" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1471,7 +1627,7 @@
       <c r="M24" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="N24" s="11" t="s">
+      <c r="N24" s="9" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1479,7 +1635,7 @@
       <c r="M25" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="N25" s="11" t="s">
+      <c r="N25" s="9" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1487,7 +1643,7 @@
       <c r="M26" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="N26" s="11" t="s">
+      <c r="N26" s="9" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1495,7 +1651,7 @@
       <c r="M27" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="N27" s="11" t="s">
+      <c r="N27" s="9" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1503,7 +1659,7 @@
       <c r="M28" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="N28" s="11" t="s">
+      <c r="N28" s="9" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1511,19 +1667,20 @@
       <c r="M29" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="N29" s="12" t="s">
+      <c r="N29" s="10" t="s">
         <v>40</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="G8:H8"/>
     <mergeCell ref="M18:N18"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="D1:E1"/>
-    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/爆チャリ仕様書.xlsx
+++ b/爆チャリ仕様書.xlsx
@@ -800,10 +800,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>

--- a/爆チャリ仕様書.xlsx
+++ b/爆チャリ仕様書.xlsx
@@ -12,7 +12,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120"/>
   </bookViews>
   <sheets>
-    <sheet name="α分" sheetId="5" r:id="rId1"/>
+    <sheet name="β分" sheetId="5" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="90">
   <si>
     <t>スクロール</t>
     <phoneticPr fontId="1"/>
@@ -207,14 +207,6 @@
     <t>ステージ１０</t>
   </si>
   <si>
-    <t>×</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>×</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ランキング</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -509,10 +501,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>〇</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ギミック</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -569,15 +557,14 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ばね</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>×</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雪玉</t>
+    <rPh sb="0" eb="2">
+      <t>ユキダマ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1103,7 +1090,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B1" s="13"/>
       <c r="D1" s="12" t="s">
@@ -1119,16 +1106,16 @@
       </c>
       <c r="K1" s="13"/>
       <c r="M1" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N1" s="13"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" s="11" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>1</v>
@@ -1149,18 +1136,18 @@
         <v>23</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>
@@ -1181,18 +1168,18 @@
         <v>23</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>6</v>
@@ -1207,24 +1194,24 @@
         <v>9</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K4" s="8" t="s">
         <v>23</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>7</v>
@@ -1245,18 +1232,18 @@
         <v>26</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>8</v>
@@ -1265,10 +1252,10 @@
         <v>25</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>28</v>
@@ -1277,18 +1264,18 @@
         <v>16</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>29</v>
@@ -1297,25 +1284,25 @@
         <v>16</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>2</v>
       </c>
       <c r="E8" s="13"/>
       <c r="G8" s="14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H8" s="15"/>
       <c r="J8" s="1" t="s">
@@ -1328,15 +1315,15 @@
         <v>28</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>18</v>
@@ -1345,10 +1332,10 @@
         <v>9</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>31</v>
@@ -1360,15 +1347,15 @@
         <v>29</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>19</v>
@@ -1377,10 +1364,10 @@
         <v>23</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>32</v>
@@ -1392,15 +1379,15 @@
         <v>30</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>20</v>
@@ -1409,30 +1396,30 @@
         <v>9</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>33</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>31</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>21</v>
@@ -1441,30 +1428,30 @@
         <v>9</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>34</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>32</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>22</v>
@@ -1473,30 +1460,30 @@
         <v>9</v>
       </c>
       <c r="G13" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H13" s="9" t="s">
         <v>88</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>93</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>35</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>33</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>3</v>
@@ -1505,170 +1492,170 @@
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="K14" s="4" t="s">
-        <v>38</v>
+      <c r="K14" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>34</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>35</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>36</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>42</v>
+        <v>75</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="M18" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N18" s="13"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M19" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M20" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N20" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M21" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M22" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N22" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M23" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M24" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N24" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M25" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M26" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N26" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M27" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M28" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N28" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="M29" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/爆チャリ仕様書.xlsx
+++ b/爆チャリ仕様書.xlsx
@@ -225,10 +225,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>×</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>BGM</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -565,6 +561,10 @@
     <rPh sb="0" eb="2">
       <t>ユキダマ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -744,7 +744,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -765,9 +765,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1089,33 +1086,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="D1" s="12" t="s">
+      <c r="A1" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="D1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="13"/>
-      <c r="G1" s="12" t="s">
+      <c r="E1" s="12"/>
+      <c r="G1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="13"/>
-      <c r="J1" s="12" t="s">
+      <c r="H1" s="12"/>
+      <c r="J1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="13"/>
-      <c r="M1" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="N1" s="13"/>
+      <c r="K1" s="12"/>
+      <c r="M1" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="N1" s="12"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>76</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>77</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>1</v>
@@ -1136,18 +1133,18 @@
         <v>23</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>77</v>
+        <v>59</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>
@@ -1168,18 +1165,18 @@
         <v>23</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>79</v>
+        <v>60</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>6</v>
@@ -1196,21 +1193,21 @@
       <c r="J4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="7" t="s">
         <v>23</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>40</v>
+        <v>43</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -1232,17 +1229,17 @@
         <v>26</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>40</v>
+        <v>44</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
@@ -1264,18 +1261,18 @@
         <v>16</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>77</v>
+        <v>63</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>29</v>
@@ -1284,27 +1281,27 @@
         <v>16</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>40</v>
+        <v>45</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E8" s="13"/>
-      <c r="G8" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="H8" s="15"/>
+      <c r="E8" s="12"/>
+      <c r="G8" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" s="14"/>
       <c r="J8" s="1" t="s">
         <v>30</v>
       </c>
@@ -1314,16 +1311,16 @@
       <c r="M8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N8" s="8" t="s">
-        <v>40</v>
+      <c r="N8" s="7" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>78</v>
+        <v>65</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>18</v>
@@ -1332,10 +1329,10 @@
         <v>9</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>88</v>
+        <v>80</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>31</v>
@@ -1346,15 +1343,15 @@
       <c r="M9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="N9" s="8" t="s">
-        <v>40</v>
+      <c r="N9" s="7" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -1364,10 +1361,10 @@
         <v>23</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>88</v>
+        <v>81</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>32</v>
@@ -1378,15 +1375,15 @@
       <c r="M10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N10" s="8" t="s">
-        <v>40</v>
+      <c r="N10" s="7" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -1396,10 +1393,10 @@
         <v>9</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>88</v>
+        <v>82</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>33</v>
@@ -1410,15 +1407,15 @@
       <c r="M11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N11" s="8" t="s">
-        <v>40</v>
+      <c r="N11" s="7" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B12" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -1428,10 +1425,10 @@
         <v>9</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>88</v>
+        <v>83</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>34</v>
@@ -1442,15 +1439,15 @@
       <c r="M12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="N12" s="8" t="s">
-        <v>40</v>
+      <c r="N12" s="7" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -1460,10 +1457,10 @@
         <v>9</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>88</v>
+        <v>84</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>35</v>
@@ -1474,15 +1471,15 @@
       <c r="M13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="N13" s="8" t="s">
-        <v>40</v>
+      <c r="N13" s="7" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B14" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
@@ -1492,10 +1489,10 @@
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>36</v>
@@ -1506,155 +1503,155 @@
       <c r="M14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N14" s="8" t="s">
-        <v>40</v>
+      <c r="N14" s="7" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B15" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15" s="8" t="s">
         <v>87</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>88</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="N15" s="8" t="s">
-        <v>40</v>
+      <c r="N15" s="7" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H16" s="10" t="s">
         <v>88</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>87</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>36</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B17" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="M18" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="N18" s="13"/>
+        <v>74</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="N18" s="12"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M19" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="N19" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="N19" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M20" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="N20" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="N20" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M21" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N21" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="N21" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M22" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N22" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="N22" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M23" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="N23" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="N23" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M24" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="N24" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N25" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="N25" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M26" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="N26" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="N26" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M27" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N27" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="N27" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M28" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N28" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="N28" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="M29" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="N29" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="N29" s="9" t="s">
         <v>38</v>
       </c>
     </row>

--- a/爆チャリ仕様書.xlsx
+++ b/爆チャリ仕様書.xlsx
@@ -211,10 +211,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>×</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>遊び方</t>
     <rPh sb="0" eb="1">
       <t>アソ</t>
@@ -561,6 +557,10 @@
     <rPh sb="0" eb="2">
       <t>ユキダマ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -744,7 +744,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -788,6 +788,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1087,7 +1090,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B1" s="12"/>
       <c r="D1" s="11" t="s">
@@ -1103,16 +1106,16 @@
       </c>
       <c r="K1" s="12"/>
       <c r="M1" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N1" s="12"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>75</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>76</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>1</v>
@@ -1133,18 +1136,18 @@
         <v>23</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>
@@ -1165,18 +1168,18 @@
         <v>23</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>6</v>
@@ -1191,21 +1194,21 @@
         <v>9</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>23</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>9</v>
@@ -1229,15 +1232,15 @@
         <v>26</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>9</v>
@@ -1251,7 +1254,7 @@
       <c r="G6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="4" t="s">
         <v>9</v>
       </c>
       <c r="J6" s="1" t="s">
@@ -1261,18 +1264,18 @@
         <v>16</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>29</v>
@@ -1281,25 +1284,25 @@
         <v>16</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>2</v>
       </c>
       <c r="E8" s="12"/>
       <c r="G8" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H8" s="14"/>
       <c r="J8" s="1" t="s">
@@ -1312,15 +1315,15 @@
         <v>28</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>18</v>
@@ -1329,10 +1332,10 @@
         <v>9</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>31</v>
@@ -1344,12 +1347,12 @@
         <v>29</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>9</v>
@@ -1361,10 +1364,10 @@
         <v>23</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>32</v>
@@ -1376,12 +1379,12 @@
         <v>30</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>9</v>
@@ -1393,10 +1396,10 @@
         <v>9</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>33</v>
@@ -1408,12 +1411,12 @@
         <v>31</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>9</v>
@@ -1425,10 +1428,10 @@
         <v>9</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>34</v>
@@ -1440,12 +1443,12 @@
         <v>32</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>9</v>
@@ -1457,10 +1460,10 @@
         <v>9</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>35</v>
@@ -1472,12 +1475,12 @@
         <v>33</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>9</v>
@@ -1489,67 +1492,67 @@
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="K14" s="4" t="s">
         <v>9</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>34</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" s="8" t="s">
         <v>86</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>87</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>35</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="N16" s="7" t="s">
-        <v>89</v>
+      <c r="N16" s="15" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>9</v>
@@ -1557,102 +1560,102 @@
     </row>
     <row r="18" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B18" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>9</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N18" s="12"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M19" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M20" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N20" s="8" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M21" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M22" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N22" s="8" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M23" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N23" s="8" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M24" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N24" s="8" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M25" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N25" s="8" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M26" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N26" s="8" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M27" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N27" s="8" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M28" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N28" s="8" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="M29" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
